--- a/punmicro/templates/writing/U07.xlsx
+++ b/punmicro/templates/writing/U07.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="Rd62a137a3b894e53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="R69b74cff78a8495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="R41086f4e36e14c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="R824b8b365e924431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="Rad28c18f780c4e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="R60b244c6fbcb4325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="R453cf8a98ca2490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="R20a5b9b2a8764ff9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -612,13 +612,13 @@
         <x:v>H3</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>Anaerobic Handling Needs</x:v>
+        <x:v>Anaerobic and Hypoxic Task Differences</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
-        <x:v>厌氧操作需求</x:v>
+        <x:v>厌氧与低氧任务的区别</x:v>
       </x:c>
       <x:c r="E10" s="3" t="str">
-        <x:v>围绕 厌氧操作需求 解释这一节问题，补充适用条件、具体例子和可核验来源。 设备参数与功能仅填受控产品资料；未知项留待确认。</x:v>
+        <x:v>说明本页主要比较厌氧工作站；微需氧微生物、细胞与组织低氧任务转到pun-IPAN低氧版本，按实际任务和使用条件选择。</x:v>
       </x:c>
       <x:c r="F10" s="3" t="str">
         <x:v>Opening a jar to inspect plates interrupts its controlled environment. A workstation allows inspection and handling within the chamber.
@@ -637,14 +637,14 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="L10" s="3" t="str">
-        <x:v>厌氧操作需求</x:v>
+        <x:v>厌氧与低氧任务的区别</x:v>
       </x:c>
       <x:c r="M10" s="3" t="str">
         <x:v>论述偏向工作站优势，未形成何时罐仍足够、何时升级的中性决策表。 按批量、观察频次、转移操作、预算与现场条件提供边界明确的选择表。
 案例有条件描述，但正文未附可复用原始数据表；长期成本的当地价格与时间假设未在本页展开。 给原始数据/方法入口与标注日期、币种、负载的成本模型。</x:v>
       </x:c>
       <x:c r="N10" s="3" t="str">
-        <x:v>何时罐足够、何时需工作站的任务决策表。</x:v>
+        <x:v>对应厌氧与低氧版本的任务资料及专业审阅；不把两类环境或气体条件视为可互换。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="134" customHeight="1">
@@ -873,7 +873,7 @@
         <x:v>已确认的配置</x:v>
       </x:c>
       <x:c r="E16" s="3" t="str">
-        <x:v>围绕 已确认的配置 解释这一节问题，补充适用条件、具体例子和可核验来源。 设备参数与功能仅填受控产品资料；未知项留待确认。</x:v>
+        <x:v>表内比较已确认的厌氧配置，并给低氧需求设置清楚的产品入口；容量和参数均对应实际型号及条件。</x:v>
       </x:c>
       <x:c r="F16" s="3" t="str">
         <x:v>Sleeved ports and the optional instant-access arrangement provide different ways to reach the working area.
@@ -899,7 +899,7 @@
 FAQ区为尚无问题的空状态。 补入口选择、气锁负载、实际布局和安装资料等具名采购问答。</x:v>
       </x:c>
       <x:c r="N16" s="3" t="str">
-        <x:v>PUN配置及已确认的安装/维护资料。</x:v>
+        <x:v>厌氧配置对照表、型号资料及pun-IPAN低氧版本说明。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="149" customHeight="1">
@@ -959,7 +959,7 @@
         <x:v>咨询 pun-IPAN</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>围绕 咨询 pun-IPAN 解释这一节问题，补充适用条件、具体例子和可核验来源。 设备参数与功能仅填受控产品资料；未知项留待确认。</x:v>
+        <x:v>读者明确版本与任务后再咨询pun-IPAN；分别收集厌氧、微需氧微生物或细胞与组织低氧培养需求。</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
         <x:v>The customer account describes a trial before purchase and a paired-sample comparison, placing the reported benefits in a specific laboratory setting.
@@ -985,7 +985,7 @@
 案例有条件描述，但正文未附可复用原始数据表；长期成本的当地价格与时间假设未在本页展开。 给原始数据/方法入口与标注日期、币种、负载的成本模型。</x:v>
       </x:c>
       <x:c r="N18" s="3" t="str">
-        <x:v>配对样本、当地运行成本及工时假设。</x:v>
+        <x:v>按版本设置的咨询字段与接收责任人。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="164" customHeight="1">
@@ -4823,10 +4823,10 @@
         <x:v>U07-003</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
-        <x:v>Anaerobic Handling Needs</x:v>
+        <x:v>Anaerobic and Hypoxic Task Differences</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>厌氧操作需求</x:v>
+        <x:v>厌氧与低氧任务的区别</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str"/>
       <x:c r="E10" s="8" t="str"/>
@@ -8698,7 +8698,7 @@
         <x:v>intent</x:v>
       </x:c>
       <x:c r="C18" s="3" t="str">
-        <x:v>比较厌氧工作环境、空间/安装要求与真实配置</x:v>
+        <x:v>比较厌氧工作站的任务、空间、转移、安装和配置；帮助低氧需求读者判断是否应转向pun-IPAN低氧版本。</x:v>
       </x:c>
       <x:c r="D18" s="3" t="str"/>
       <x:c r="E18" s="8" t="str"/>
@@ -8742,9 +8742,7 @@
       <x:c r="C20" s="3" t="str">
         <x:v>Find Anaerobic Workstation Selection Guide by laboratory task. Explore available information, related pages and the next steps for your requirements.</x:v>
       </x:c>
-      <x:c r="D20" s="3" t="str">
-        <x:v>根据实验室任务查找厌氧工作站选型指南，了解现有资料、相关页面及满足需求的后续步骤。</x:v>
-      </x:c>
+      <x:c r="D20" s="3" t="str"/>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="3" t="str">
         <x:v>准确摘要，不固定字符数；搜索引擎可能重新生成片段。</x:v>
@@ -8864,9 +8862,7 @@
       <x:c r="C26" s="3" t="str">
         <x:v>Find Anaerobic Workstation Selection Guide by laboratory task. Explore available information, related pages and the next steps for your requirements.</x:v>
       </x:c>
-      <x:c r="D26" s="3" t="str">
-        <x:v>根据实验室任务查找厌氧工作站选型指南，了解现有资料、相关页面及满足需求的后续步骤。</x:v>
-      </x:c>
+      <x:c r="D26" s="3" t="str"/>
       <x:c r="E26" s="8" t="str"/>
       <x:c r="F26" s="3" t="str">
         <x:v>可编辑，需与内容相符。</x:v>
@@ -9000,9 +8996,7 @@
       <x:c r="C33" s="3" t="str">
         <x:v>Find Anaerobic Workstation Selection Guide by laboratory task. Explore available information, related pages and the next steps for your requirements.</x:v>
       </x:c>
-      <x:c r="D33" s="3" t="str">
-        <x:v>根据实验室任务查找厌氧工作站选型指南，了解现有资料、相关页面及满足需求的后续步骤。</x:v>
-      </x:c>
+      <x:c r="D33" s="3" t="str"/>
       <x:c r="E33" s="8" t="str"/>
       <x:c r="F33" s="3" t="str">
         <x:v>可沿用已审核摘要。</x:v>
